--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/162.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/162.xlsx
@@ -426,13 +426,13 @@
         <v>-15.36510733867306</v>
       </c>
       <c r="E2">
-        <v>-10.97796952236815</v>
+        <v>-10.52763995314938</v>
       </c>
       <c r="F2">
-        <v>-1.034179573109564</v>
+        <v>-0.5074058310561085</v>
       </c>
       <c r="G2">
-        <v>-10.98025968913712</v>
+        <v>-14.65399028206682</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.13711469507344</v>
       </c>
       <c r="E3">
-        <v>-11.69565114005177</v>
+        <v>-11.62248911398384</v>
       </c>
       <c r="F3">
-        <v>-0.8827523551430093</v>
+        <v>-0.7480200538124753</v>
       </c>
       <c r="G3">
-        <v>-11.99327338197195</v>
+        <v>-15.25360456650347</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.77266322161163</v>
       </c>
       <c r="E4">
-        <v>-13.11429524938267</v>
+        <v>-12.32310744160655</v>
       </c>
       <c r="F4">
-        <v>-0.3453937344165812</v>
+        <v>-0.6308922165262364</v>
       </c>
       <c r="G4">
-        <v>-11.7011541541322</v>
+        <v>-15.13069063172141</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.27711758068713</v>
       </c>
       <c r="E5">
-        <v>-12.49180215534029</v>
+        <v>-12.07320360349327</v>
       </c>
       <c r="F5">
-        <v>-0.5648978422800054</v>
+        <v>-0.1274809203339349</v>
       </c>
       <c r="G5">
-        <v>-11.04611968209538</v>
+        <v>-14.36660844489377</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.68155740804625</v>
       </c>
       <c r="E6">
-        <v>-14.20306719809884</v>
+        <v>-12.75107087770144</v>
       </c>
       <c r="F6">
-        <v>-0.4378759847347292</v>
+        <v>0.02264493244282233</v>
       </c>
       <c r="G6">
-        <v>-10.87957937819681</v>
+        <v>-13.68667867040164</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.00947857546267</v>
       </c>
       <c r="E7">
-        <v>-15.35419623390063</v>
+        <v>-14.32922142700452</v>
       </c>
       <c r="F7">
-        <v>-0.5149986466701688</v>
+        <v>0.1572811431546316</v>
       </c>
       <c r="G7">
-        <v>-9.858782592799153</v>
+        <v>-13.57415819334012</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.28119833628618</v>
       </c>
       <c r="E8">
-        <v>-16.25888118573099</v>
+        <v>-14.90541993126649</v>
       </c>
       <c r="F8">
-        <v>-0.09163166424298066</v>
+        <v>0.1158735417908927</v>
       </c>
       <c r="G8">
-        <v>-10.63163275948755</v>
+        <v>-13.66136789448114</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.50926895132685</v>
       </c>
       <c r="E9">
-        <v>-16.23673241935948</v>
+        <v>-15.70164793061315</v>
       </c>
       <c r="F9">
-        <v>-0.9147513595457514</v>
+        <v>0.2873919827449471</v>
       </c>
       <c r="G9">
-        <v>-9.559393406955165</v>
+        <v>-12.98703625249591</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.7273552788367</v>
       </c>
       <c r="E10">
-        <v>-18.16936285703498</v>
+        <v>-16.04575308503399</v>
       </c>
       <c r="F10">
-        <v>-0.2658083361926187</v>
+        <v>-0.03987692565087315</v>
       </c>
       <c r="G10">
-        <v>-8.069568461190187</v>
+        <v>-12.21684445387555</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.954974525715562</v>
       </c>
       <c r="E11">
-        <v>-17.9293809054725</v>
+        <v>-18.18245467539115</v>
       </c>
       <c r="F11">
-        <v>-0.04797835885025232</v>
+        <v>0.539582639955437</v>
       </c>
       <c r="G11">
-        <v>-8.377015514876764</v>
+        <v>-11.30736807278143</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.208338734472655</v>
       </c>
       <c r="E12">
-        <v>-18.2638947519451</v>
+        <v>-18.54395822694947</v>
       </c>
       <c r="F12">
-        <v>-0.3287982218688959</v>
+        <v>0.5555709591968703</v>
       </c>
       <c r="G12">
-        <v>-7.520650215869171</v>
+        <v>-10.33939435200839</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.493557353072905</v>
       </c>
       <c r="E13">
-        <v>-18.9924945204612</v>
+        <v>-18.13986890582302</v>
       </c>
       <c r="F13">
-        <v>0.7368102916227769</v>
+        <v>0.7710781943417868</v>
       </c>
       <c r="G13">
-        <v>-7.791936180630288</v>
+        <v>-10.25162847921677</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.837218337727879</v>
       </c>
       <c r="E14">
-        <v>-20.54348328266628</v>
+        <v>-19.73834324647253</v>
       </c>
       <c r="F14">
-        <v>0.3551996532359062</v>
+        <v>0.7437536671930424</v>
       </c>
       <c r="G14">
-        <v>-8.277861365430052</v>
+        <v>-8.812951462033533</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.249416759422846</v>
       </c>
       <c r="E15">
-        <v>-23.14182204183936</v>
+        <v>-20.27041177152975</v>
       </c>
       <c r="F15">
-        <v>0.4030039076840629</v>
+        <v>0.1261444692182038</v>
       </c>
       <c r="G15">
-        <v>-5.60708868325964</v>
+        <v>-7.707904603206967</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.734452609208184</v>
       </c>
       <c r="E16">
-        <v>-22.77268348310411</v>
+        <v>-20.7784703273983</v>
       </c>
       <c r="F16">
-        <v>0.552320445508285</v>
+        <v>0.6515240689327482</v>
       </c>
       <c r="G16">
-        <v>-5.185381460830659</v>
+        <v>-6.886505286185158</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.284511642151537</v>
       </c>
       <c r="E17">
-        <v>-21.76180128731987</v>
+        <v>-21.50661272003963</v>
       </c>
       <c r="F17">
-        <v>0.08451735049272301</v>
+        <v>0.9896545307140756</v>
       </c>
       <c r="G17">
-        <v>-5.475818931536459</v>
+        <v>-7.070773561446531</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.906031283415341</v>
       </c>
       <c r="E18">
-        <v>-22.12188289803978</v>
+        <v>-22.56919197509544</v>
       </c>
       <c r="F18">
-        <v>0.2733312744498283</v>
+        <v>0.5461623622358734</v>
       </c>
       <c r="G18">
-        <v>-4.311112731546688</v>
+        <v>-6.926178863927784</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.591923572751766</v>
       </c>
       <c r="E19">
-        <v>-23.9636630901734</v>
+        <v>-23.69213578867349</v>
       </c>
       <c r="F19">
-        <v>0.390125279672739</v>
+        <v>0.4078763647473296</v>
       </c>
       <c r="G19">
-        <v>-3.285207774381939</v>
+        <v>-6.201205806828326</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.331840885469272</v>
       </c>
       <c r="E20">
-        <v>-25.76605008691429</v>
+        <v>-23.55602797389895</v>
       </c>
       <c r="F20">
-        <v>0.3961980411026622</v>
+        <v>1.075373989555768</v>
       </c>
       <c r="G20">
-        <v>-4.166223395474945</v>
+        <v>-5.31760133912361</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.108790365255794</v>
       </c>
       <c r="E21">
-        <v>-26.17210476576007</v>
+        <v>-24.42419531133145</v>
       </c>
       <c r="F21">
-        <v>0.7093010385432081</v>
+        <v>0.6396535640506313</v>
       </c>
       <c r="G21">
-        <v>-3.418645933433343</v>
+        <v>-4.596822743222408</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.921409316388997</v>
       </c>
       <c r="E22">
-        <v>-24.62192207192836</v>
+        <v>-24.09896936504858</v>
       </c>
       <c r="F22">
-        <v>1.039952999412062</v>
+        <v>0.9648863453703704</v>
       </c>
       <c r="G22">
-        <v>-1.695440769331905</v>
+        <v>-4.750544614792927</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.764541020654189</v>
       </c>
       <c r="E23">
-        <v>-27.58713968130687</v>
+        <v>-25.19221091761032</v>
       </c>
       <c r="F23">
-        <v>0.8030117577197078</v>
+        <v>1.219867772360892</v>
       </c>
       <c r="G23">
-        <v>-1.630269369845812</v>
+        <v>-2.973602675498039</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.635780987385869</v>
       </c>
       <c r="E24">
-        <v>-24.80011299565619</v>
+        <v>-26.15065791285975</v>
       </c>
       <c r="F24">
-        <v>0.7437337863753751</v>
+        <v>0.8461663859359508</v>
       </c>
       <c r="G24">
-        <v>-1.865678952597847</v>
+        <v>-2.900144980527151</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.530564298776302</v>
       </c>
       <c r="E25">
-        <v>-27.29046123516835</v>
+        <v>-25.65750709342444</v>
       </c>
       <c r="F25">
-        <v>1.086603338068119</v>
+        <v>0.8145625127843441</v>
       </c>
       <c r="G25">
-        <v>-1.453247878769903</v>
+        <v>-3.158645618415602</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.458117453039458</v>
       </c>
       <c r="E26">
-        <v>-27.1036345115079</v>
+        <v>-25.58132910366741</v>
       </c>
       <c r="F26">
-        <v>0.7724466572912116</v>
+        <v>0.9281068326860723</v>
       </c>
       <c r="G26">
-        <v>-2.197094355988746</v>
+        <v>-2.30073429464117</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.425767052996935</v>
       </c>
       <c r="E27">
-        <v>-27.18509270195788</v>
+        <v>-26.5607112342543</v>
       </c>
       <c r="F27">
-        <v>0.5717282653884747</v>
+        <v>0.8565358890841951</v>
       </c>
       <c r="G27">
-        <v>-1.394902824185788</v>
+        <v>-2.129489705531289</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.440042393388412</v>
       </c>
       <c r="E28">
-        <v>-27.06415074663503</v>
+        <v>-26.11433955131823</v>
       </c>
       <c r="F28">
-        <v>0.4487082507661229</v>
+        <v>0.9305107548889965</v>
       </c>
       <c r="G28">
-        <v>-0.9332075221879496</v>
+        <v>-2.102167773195684</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.501634785501555</v>
       </c>
       <c r="E29">
-        <v>-26.48889869344066</v>
+        <v>-26.00797475382607</v>
       </c>
       <c r="F29">
-        <v>0.5699075138371213</v>
+        <v>1.2220894537352</v>
       </c>
       <c r="G29">
-        <v>-1.906401973276422</v>
+        <v>-2.150677196982625</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.618355406955837</v>
       </c>
       <c r="E30">
-        <v>-26.0174981346642</v>
+        <v>-25.33096788967935</v>
       </c>
       <c r="F30">
-        <v>0.953827640542997</v>
+        <v>0.497448560379443</v>
       </c>
       <c r="G30">
-        <v>-0.9162244235714884</v>
+        <v>-2.328450181895948</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.794981239032886</v>
       </c>
       <c r="E31">
-        <v>-26.23279084593686</v>
+        <v>-24.48271678093258</v>
       </c>
       <c r="F31">
-        <v>0.868348408248116</v>
+        <v>0.4480223625566049</v>
       </c>
       <c r="G31">
-        <v>-0.8792555615344471</v>
+        <v>-2.184679810216479</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.030879012668878</v>
       </c>
       <c r="E32">
-        <v>-25.81897436264194</v>
+        <v>-24.61359420822826</v>
       </c>
       <c r="F32">
-        <v>0.2076309706315911</v>
+        <v>0.4167755157556047</v>
       </c>
       <c r="G32">
-        <v>-0.6602729057482758</v>
+        <v>-2.555500637161324</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.31662014020728</v>
       </c>
       <c r="E33">
-        <v>-25.36011314839272</v>
+        <v>-24.14091661978163</v>
       </c>
       <c r="F33">
-        <v>0.932318252561905</v>
+        <v>0.5304614864832117</v>
       </c>
       <c r="G33">
-        <v>-1.841581491617492</v>
+        <v>-2.773963537297829</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.645921064146453</v>
       </c>
       <c r="E34">
-        <v>-23.90774549312669</v>
+        <v>-23.37750194309456</v>
       </c>
       <c r="F34">
-        <v>0.1721519947696883</v>
+        <v>-0.3321348857673723</v>
       </c>
       <c r="G34">
-        <v>-2.966299612038406</v>
+        <v>-2.749323146849034</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.009391246953983</v>
       </c>
       <c r="E35">
-        <v>-23.04807357293257</v>
+        <v>-22.15592796562945</v>
       </c>
       <c r="F35">
-        <v>0.3541931868415049</v>
+        <v>0.2918925028443569</v>
       </c>
       <c r="G35">
-        <v>-0.5104607884596368</v>
+        <v>-3.079838081853251</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.391487223884649</v>
       </c>
       <c r="E36">
-        <v>-23.28803741059902</v>
+        <v>-21.59659802704605</v>
       </c>
       <c r="F36">
-        <v>0.8649620423054716</v>
+        <v>0.3246022464787009</v>
       </c>
       <c r="G36">
-        <v>-2.830653319112309</v>
+        <v>-3.580978533951506</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.769135985013951</v>
       </c>
       <c r="E37">
-        <v>-23.03964155433029</v>
+        <v>-21.45586211183567</v>
       </c>
       <c r="F37">
-        <v>0.2505428871988139</v>
+        <v>0.4965042215402515</v>
       </c>
       <c r="G37">
-        <v>-3.092729346183173</v>
+        <v>-4.416705892067281</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.12483252541116</v>
       </c>
       <c r="E38">
-        <v>-23.54645025137272</v>
+        <v>-21.34200721833482</v>
       </c>
       <c r="F38">
-        <v>0.9850504646893159</v>
+        <v>0.1299988627434299</v>
       </c>
       <c r="G38">
-        <v>-3.274183657736166</v>
+        <v>-4.600100183306287</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.443261032228844</v>
       </c>
       <c r="E39">
-        <v>-20.38846908890972</v>
+        <v>-21.42236498960093</v>
       </c>
       <c r="F39">
-        <v>0.4082019131366298</v>
+        <v>0.2855422383344958</v>
       </c>
       <c r="G39">
-        <v>-2.831600135136541</v>
+        <v>-5.036569128294879</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.710633433604018</v>
       </c>
       <c r="E40">
-        <v>-20.6934527563783</v>
+        <v>-20.23719994315749</v>
       </c>
       <c r="F40">
-        <v>0.7349779429277844</v>
+        <v>0.2388703621259661</v>
       </c>
       <c r="G40">
-        <v>-4.306560731430189</v>
+        <v>-5.732925829752877</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.911509151497117</v>
       </c>
       <c r="E41">
-        <v>-20.09120646962421</v>
+        <v>-18.7809559141409</v>
       </c>
       <c r="F41">
-        <v>1.280269009903421</v>
+        <v>0.3632447574518951</v>
       </c>
       <c r="G41">
-        <v>-3.676232860752956</v>
+        <v>-6.204297856362005</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.040965805770792</v>
       </c>
       <c r="E42">
-        <v>-19.07643431466738</v>
+        <v>-17.36989247029883</v>
       </c>
       <c r="F42">
-        <v>1.218176246124375</v>
+        <v>0.6508862260325926</v>
       </c>
       <c r="G42">
-        <v>-4.713413536024461</v>
+        <v>-5.914671469313325</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.103068130610781</v>
       </c>
       <c r="E43">
-        <v>-18.70836447579794</v>
+        <v>-17.40121139653588</v>
       </c>
       <c r="F43">
-        <v>1.034871793763289</v>
+        <v>1.121799012278264</v>
       </c>
       <c r="G43">
-        <v>-4.870869702963278</v>
+        <v>-6.576959346626684</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.101675742381712</v>
       </c>
       <c r="E44">
-        <v>-19.09151413311292</v>
+        <v>-17.05836515788916</v>
       </c>
       <c r="F44">
-        <v>1.198780851755228</v>
+        <v>0.6153641750657441</v>
       </c>
       <c r="G44">
-        <v>-6.403900578561283</v>
+        <v>-7.433751706008842</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.040188517569876</v>
       </c>
       <c r="E45">
-        <v>-16.96775039299568</v>
+        <v>-15.8230019770707</v>
       </c>
       <c r="F45">
-        <v>1.484551038373001</v>
+        <v>1.240379805989013</v>
       </c>
       <c r="G45">
-        <v>-6.80168910946903</v>
+        <v>-6.939245587171287</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.929258752152837</v>
       </c>
       <c r="E46">
-        <v>-15.05256816567173</v>
+        <v>-15.00046807221348</v>
       </c>
       <c r="F46">
-        <v>1.172667397749376</v>
+        <v>0.8952256169993488</v>
       </c>
       <c r="G46">
-        <v>-7.186583065501316</v>
+        <v>-7.691888183887974</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.783483394738387</v>
       </c>
       <c r="E47">
-        <v>-15.98267597058115</v>
+        <v>-14.70348621831645</v>
       </c>
       <c r="F47">
-        <v>1.180227078667324</v>
+        <v>0.8046204472159444</v>
       </c>
       <c r="G47">
-        <v>-6.890001222274628</v>
+        <v>-8.392227471629715</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.614233996735587</v>
       </c>
       <c r="E48">
-        <v>-15.29432980751923</v>
+        <v>-14.37817423102744</v>
       </c>
       <c r="F48">
-        <v>1.328248049873568</v>
+        <v>1.511083646284669</v>
       </c>
       <c r="G48">
-        <v>-7.084681163257009</v>
+        <v>-9.285121330117624</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.42745469283592</v>
       </c>
       <c r="E49">
-        <v>-14.23506539543704</v>
+        <v>-13.55718453580684</v>
       </c>
       <c r="F49">
-        <v>1.708006458747779</v>
+        <v>1.330383581037985</v>
       </c>
       <c r="G49">
-        <v>-7.385334977497001</v>
+        <v>-9.0734682221554</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.232635524177256</v>
       </c>
       <c r="E50">
-        <v>-13.37482741599196</v>
+        <v>-12.55720690543307</v>
       </c>
       <c r="F50">
-        <v>1.393679134285895</v>
+        <v>1.135710614440879</v>
       </c>
       <c r="G50">
-        <v>-7.409998541764571</v>
+        <v>-9.477795080503208</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.039212022772953</v>
       </c>
       <c r="E51">
-        <v>-12.14134355188668</v>
+        <v>-12.86737567564044</v>
       </c>
       <c r="F51">
-        <v>0.9853453634847126</v>
+        <v>1.307724419101807</v>
       </c>
       <c r="G51">
-        <v>-8.827153702397005</v>
+        <v>-9.597375295927222</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.850233632671192</v>
       </c>
       <c r="E52">
-        <v>-12.91992408802545</v>
+        <v>-11.54233512404808</v>
       </c>
       <c r="F52">
-        <v>1.532223582404113</v>
+        <v>1.161467870463527</v>
       </c>
       <c r="G52">
-        <v>-10.02684243710026</v>
+        <v>-10.36992420297155</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.661774291986124</v>
       </c>
       <c r="E53">
-        <v>-12.53607251723928</v>
+        <v>-11.29782922695193</v>
       </c>
       <c r="F53">
-        <v>1.62626813364394</v>
+        <v>1.384035280982503</v>
       </c>
       <c r="G53">
-        <v>-8.808942391385475</v>
+        <v>-11.79175385390543</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.472533119201187</v>
       </c>
       <c r="E54">
-        <v>-10.91268704107357</v>
+        <v>-10.00581483629751</v>
       </c>
       <c r="F54">
-        <v>1.773046553745985</v>
+        <v>1.12628379339702</v>
       </c>
       <c r="G54">
-        <v>-8.664420525868591</v>
+        <v>-11.43817434812911</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.280840783044228</v>
       </c>
       <c r="E55">
-        <v>-11.55227059602091</v>
+        <v>-9.793388649071701</v>
       </c>
       <c r="F55">
-        <v>1.736230592895964</v>
+        <v>1.225835331130659</v>
       </c>
       <c r="G55">
-        <v>-8.76490551462209</v>
+        <v>-10.34064904876777</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.080149754139248</v>
       </c>
       <c r="E56">
-        <v>-11.23400038581382</v>
+        <v>-10.4645990664886</v>
       </c>
       <c r="F56">
-        <v>1.146022131870927</v>
+        <v>1.024195794676009</v>
       </c>
       <c r="G56">
-        <v>-9.036688061214097</v>
+        <v>-11.32968446026166</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.859210841102964</v>
       </c>
       <c r="E57">
-        <v>-9.389770289242049</v>
+        <v>-9.350965795470323</v>
       </c>
       <c r="F57">
-        <v>1.94769291001301</v>
+        <v>1.503242320449769</v>
       </c>
       <c r="G57">
-        <v>-8.888461695238769</v>
+        <v>-11.78446072208242</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.614053184906559</v>
       </c>
       <c r="E58">
-        <v>-9.20343264077443</v>
+        <v>-8.744480857045055</v>
       </c>
       <c r="F58">
-        <v>1.395836203002785</v>
+        <v>1.246262871283695</v>
       </c>
       <c r="G58">
-        <v>-9.449185345952827</v>
+        <v>-11.91114867877925</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.342786706999572</v>
       </c>
       <c r="E59">
-        <v>-9.640602464526911</v>
+        <v>-9.892181838023038</v>
       </c>
       <c r="F59">
-        <v>1.405178530571558</v>
+        <v>0.9533041123444277</v>
       </c>
       <c r="G59">
-        <v>-8.779786416821114</v>
+        <v>-11.62398202706625</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.040094218099148</v>
       </c>
       <c r="E60">
-        <v>-7.66120194730019</v>
+        <v>-8.784363127630607</v>
       </c>
       <c r="F60">
-        <v>1.000416680011247</v>
+        <v>0.9101826188242966</v>
       </c>
       <c r="G60">
-        <v>-8.872004973363053</v>
+        <v>-10.98492424780195</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.701537489449608</v>
       </c>
       <c r="E61">
-        <v>-11.19605177362954</v>
+        <v>-9.328278140691895</v>
       </c>
       <c r="F61">
-        <v>1.053950751784568</v>
+        <v>0.8492412857351426</v>
       </c>
       <c r="G61">
-        <v>-10.20962096686896</v>
+        <v>-11.59220741098032</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.328616701134587</v>
       </c>
       <c r="E62">
-        <v>-7.403798956230199</v>
+        <v>-8.242164406218228</v>
       </c>
       <c r="F62">
-        <v>1.366253546314009</v>
+        <v>0.9195000953709854</v>
       </c>
       <c r="G62">
-        <v>-8.873855568319504</v>
+        <v>-11.55598011114408</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.924651729380232</v>
       </c>
       <c r="E63">
-        <v>-8.653408716276797</v>
+        <v>-9.192537132311974</v>
       </c>
       <c r="F63">
-        <v>0.6444166766167284</v>
+        <v>0.9349259531459179</v>
       </c>
       <c r="G63">
-        <v>-9.805257692520218</v>
+        <v>-11.64638117818496</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.490913489698459</v>
       </c>
       <c r="E64">
-        <v>-8.083699515267819</v>
+        <v>-7.630920041610898</v>
       </c>
       <c r="F64">
-        <v>1.172120675263528</v>
+        <v>0.4336659270986866</v>
       </c>
       <c r="G64">
-        <v>-9.533408935017425</v>
+        <v>-11.67587813893986</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.028464170105546</v>
       </c>
       <c r="E65">
-        <v>-10.14420500197192</v>
+        <v>-7.670394749535761</v>
       </c>
       <c r="F65">
-        <v>0.9007176928799094</v>
+        <v>0.4871030798858799</v>
       </c>
       <c r="G65">
-        <v>-8.455700561254162</v>
+        <v>-10.99076736067877</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.543511149253262</v>
       </c>
       <c r="E66">
-        <v>-7.335477868876477</v>
+        <v>-8.302356882728182</v>
       </c>
       <c r="F66">
-        <v>0.8714415321301694</v>
+        <v>0.5783750854285379</v>
       </c>
       <c r="G66">
-        <v>-8.565100849144917</v>
+        <v>-10.34585984744658</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.040909132785121</v>
       </c>
       <c r="E67">
-        <v>-9.184625888220575</v>
+        <v>-7.521172474035007</v>
       </c>
       <c r="F67">
-        <v>0.6431451326534312</v>
+        <v>0.3161205926414368</v>
       </c>
       <c r="G67">
-        <v>-8.340652482673409</v>
+        <v>-11.17904139604266</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.522885776101481</v>
       </c>
       <c r="E68">
-        <v>-8.320796828887415</v>
+        <v>-7.683531852632012</v>
       </c>
       <c r="F68">
-        <v>-0.01499028376856761</v>
+        <v>0.2579244691251603</v>
       </c>
       <c r="G68">
-        <v>-8.894248528841414</v>
+        <v>-10.10377289434184</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.9910888589003912</v>
       </c>
       <c r="E69">
-        <v>-8.244247504261756</v>
+        <v>-8.322359152420063</v>
       </c>
       <c r="F69">
-        <v>0.4956650853612156</v>
+        <v>0.2307391077000861</v>
       </c>
       <c r="G69">
-        <v>-7.486697260818406</v>
+        <v>-10.42615712950161</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.4520160909363306</v>
       </c>
       <c r="E70">
-        <v>-7.996417707243981</v>
+        <v>-7.63002340375738</v>
       </c>
       <c r="F70">
-        <v>0.09960937620432719</v>
+        <v>-0.087721770101767</v>
       </c>
       <c r="G70">
-        <v>-9.121967714305724</v>
+        <v>-9.764928626760815</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.09022088629420121</v>
       </c>
       <c r="E71">
-        <v>-9.232704696760011</v>
+        <v>-6.250962685727518</v>
       </c>
       <c r="F71">
-        <v>0.3738826516386463</v>
+        <v>-0.2570119027422907</v>
       </c>
       <c r="G71">
-        <v>-6.611590963513</v>
+        <v>-9.644735960412037</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.6325515424598172</v>
       </c>
       <c r="E72">
-        <v>-9.108624508949843</v>
+        <v>-8.788814617580147</v>
       </c>
       <c r="F72">
-        <v>0.1043633767289936</v>
+        <v>-0.3721359192811576</v>
       </c>
       <c r="G72">
-        <v>-7.197676703603413</v>
+        <v>-9.030450993418111</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.171583346675819</v>
       </c>
       <c r="E73">
-        <v>-9.974332884996185</v>
+        <v>-8.931556646775924</v>
       </c>
       <c r="F73">
-        <v>0.2521341809795918</v>
+        <v>-0.3954271255456713</v>
       </c>
       <c r="G73">
-        <v>-7.9478661860755</v>
+        <v>-8.77834632951153</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.699120621525</v>
       </c>
       <c r="E74">
-        <v>-8.20686042285443</v>
+        <v>-9.32933780360969</v>
       </c>
       <c r="F74">
-        <v>-0.100727966693122</v>
+        <v>-0.242930485262102</v>
       </c>
       <c r="G74">
-        <v>-5.443074325607527</v>
+        <v>-8.184911178323935</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>2.21160398898977</v>
       </c>
       <c r="E75">
-        <v>-8.66135165968625</v>
+        <v>-9.179920803726606</v>
       </c>
       <c r="F75">
-        <v>0.1156705917772068</v>
+        <v>-0.1353247312710434</v>
       </c>
       <c r="G75">
-        <v>-5.912638794352214</v>
+        <v>-7.733306419129796</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.70620159506294</v>
       </c>
       <c r="E76">
-        <v>-9.422905133556174</v>
+        <v>-10.10697188868085</v>
       </c>
       <c r="F76">
-        <v>-0.006275030323714007</v>
+        <v>-0.2710784096092292</v>
       </c>
       <c r="G76">
-        <v>-6.089236535599095</v>
+        <v>-7.694394266861202</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>3.179802318342163</v>
       </c>
       <c r="E77">
-        <v>-9.02745614083636</v>
+        <v>-9.7838833821296</v>
       </c>
       <c r="F77">
-        <v>-0.1977355881327637</v>
+        <v>-0.6515492144498477</v>
       </c>
       <c r="G77">
-        <v>-4.49693034212044</v>
+        <v>-6.510463728924883</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.625512958663888</v>
       </c>
       <c r="E78">
-        <v>-10.86388367669291</v>
+        <v>-11.62928182499535</v>
       </c>
       <c r="F78">
-        <v>0.1575984078699038</v>
+        <v>-0.7789156728346884</v>
       </c>
       <c r="G78">
-        <v>-4.324119864970484</v>
+        <v>-6.945485965512813</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>4.042941210516019</v>
       </c>
       <c r="E79">
-        <v>-11.56201587208541</v>
+        <v>-11.7724812300659</v>
       </c>
       <c r="F79">
-        <v>-0.004669654297088565</v>
+        <v>-1.115565842067213</v>
       </c>
       <c r="G79">
-        <v>-4.042385818487428</v>
+        <v>-6.362863056056477</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>4.431769643319365</v>
       </c>
       <c r="E80">
-        <v>-11.85020795793355</v>
+        <v>-11.88012758570223</v>
       </c>
       <c r="F80">
-        <v>-0.2058038866360309</v>
+        <v>-0.3108259626977579</v>
       </c>
       <c r="G80">
-        <v>-2.884118629571538</v>
+        <v>-5.25128449088093</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>4.79288264431348</v>
       </c>
       <c r="E81">
-        <v>-12.36271800375165</v>
+        <v>-12.66385246831371</v>
       </c>
       <c r="F81">
-        <v>-0.3144450998805889</v>
+        <v>-0.8676114557546399</v>
       </c>
       <c r="G81">
-        <v>-2.506570774090895</v>
+        <v>-4.490865422692495</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>5.120094099344375</v>
       </c>
       <c r="E82">
-        <v>-14.41379067909777</v>
+        <v>-14.13834171910721</v>
       </c>
       <c r="F82">
-        <v>-0.9026613373018926</v>
+        <v>-0.4447953376503135</v>
       </c>
       <c r="G82">
-        <v>-1.652850600969181</v>
+        <v>-4.094036949991136</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>5.417085963516052</v>
       </c>
       <c r="E83">
-        <v>-15.52764584534242</v>
+        <v>-15.65460161414746</v>
       </c>
       <c r="F83">
-        <v>-0.8077362315128889</v>
+        <v>-1.042879087573765</v>
       </c>
       <c r="G83">
-        <v>-1.960161922288647</v>
+        <v>-2.753782451690432</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>5.685545351369989</v>
       </c>
       <c r="E84">
-        <v>-14.66592705489684</v>
+        <v>-15.90018075958342</v>
       </c>
       <c r="F84">
-        <v>-0.2857098630448768</v>
+        <v>-0.7363508422092386</v>
       </c>
       <c r="G84">
-        <v>-0.6775109163712609</v>
+        <v>-1.655661254132022</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>5.923428291155611</v>
       </c>
       <c r="E85">
-        <v>-17.76814458842939</v>
+        <v>-16.81061687340353</v>
       </c>
       <c r="F85">
-        <v>-1.345499923899286</v>
+        <v>-0.8877656346647519</v>
       </c>
       <c r="G85">
-        <v>0.09702100745108677</v>
+        <v>-2.214103938969522</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>6.125485615532621</v>
       </c>
       <c r="E86">
-        <v>-18.93710222639938</v>
+        <v>-18.87764336267867</v>
       </c>
       <c r="F86">
-        <v>-0.8264449093051157</v>
+        <v>-0.9266607976957999</v>
       </c>
       <c r="G86">
-        <v>-0.2199537962975116</v>
+        <v>-1.398756299193499</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>6.293116485367332</v>
       </c>
       <c r="E87">
-        <v>-20.42477839350321</v>
+        <v>-19.23336405292919</v>
       </c>
       <c r="F87">
-        <v>-0.874737900520924</v>
+        <v>-0.8529634349709363</v>
       </c>
       <c r="G87">
-        <v>-0.2263332175516872</v>
+        <v>-1.396882530418272</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>6.422683312611763</v>
       </c>
       <c r="E88">
-        <v>-19.39503963195104</v>
+        <v>-21.34587453513737</v>
       </c>
       <c r="F88">
-        <v>-0.9907888601835236</v>
+        <v>-1.127676573496142</v>
       </c>
       <c r="G88">
-        <v>-0.03104744673561911</v>
+        <v>-0.6141834907505423</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>6.508138267409378</v>
       </c>
       <c r="E89">
-        <v>-21.79451045507728</v>
+        <v>-21.23127697189927</v>
       </c>
       <c r="F89">
-        <v>-1.34193545896504</v>
+        <v>-0.8019865333700575</v>
       </c>
       <c r="G89">
-        <v>-0.01975517590116509</v>
+        <v>-0.9060279433105332</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>6.54016962531441</v>
       </c>
       <c r="E90">
-        <v>-25.28994897211787</v>
+        <v>-23.56148478507819</v>
       </c>
       <c r="F90">
-        <v>-1.05955743686173</v>
+        <v>-1.356314260342834</v>
       </c>
       <c r="G90">
-        <v>0.6681894293415447</v>
+        <v>0.1482252153069942</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>6.517106920180523</v>
       </c>
       <c r="E91">
-        <v>-26.00068391067372</v>
+        <v>-24.9768865070196</v>
       </c>
       <c r="F91">
-        <v>-1.943239072983173</v>
+        <v>-1.161821049472135</v>
       </c>
       <c r="G91">
-        <v>1.973852037302404</v>
+        <v>-0.6292961311373153</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>6.433467847906424</v>
       </c>
       <c r="E92">
-        <v>-27.21476779213014</v>
+        <v>-27.15668558450776</v>
       </c>
       <c r="F92">
-        <v>-1.751567281486409</v>
+        <v>-1.612732904777212</v>
       </c>
       <c r="G92">
-        <v>1.051090436959189</v>
+        <v>0.1040592272675773</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>6.283576162756489</v>
       </c>
       <c r="E93">
-        <v>-27.57914239620932</v>
+        <v>-28.11002898955054</v>
       </c>
       <c r="F93">
-        <v>-1.432590330792612</v>
+        <v>-1.28240980576727</v>
       </c>
       <c r="G93">
-        <v>0.1388894768862495</v>
+        <v>-0.5318965708264177</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>6.061297206205201</v>
       </c>
       <c r="E94">
-        <v>-29.61492015059454</v>
+        <v>-30.25817176948808</v>
       </c>
       <c r="F94">
-        <v>-1.70658527477959</v>
+        <v>-1.428194184985955</v>
       </c>
       <c r="G94">
-        <v>0.4214180542987311</v>
+        <v>0.3262001434982132</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>5.77177235267433</v>
       </c>
       <c r="E95">
-        <v>-32.6844375733177</v>
+        <v>-32.18666091768357</v>
       </c>
       <c r="F95">
-        <v>-2.168394303268495</v>
+        <v>-1.356655547712787</v>
       </c>
       <c r="G95">
-        <v>1.245316833202691</v>
+        <v>-0.3810217684196727</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>5.410302988123955</v>
       </c>
       <c r="E96">
-        <v>-34.30524181929903</v>
+        <v>-33.33883603098113</v>
       </c>
       <c r="F96">
-        <v>-2.693515452353366</v>
+        <v>-1.871271341395355</v>
       </c>
       <c r="G96">
-        <v>0.3464474400163958</v>
+        <v>-0.02723038772883943</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.98752449079059</v>
       </c>
       <c r="E97">
-        <v>-35.21672627485191</v>
+        <v>-36.60049207737574</v>
       </c>
       <c r="F97">
-        <v>-2.379902180592696</v>
+        <v>-1.89322556267175</v>
       </c>
       <c r="G97">
-        <v>-0.8155275599034767</v>
+        <v>-1.200603595940423</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.488751231748887</v>
       </c>
       <c r="E98">
-        <v>-37.50980060116793</v>
+        <v>-38.20610102882433</v>
       </c>
       <c r="F98">
-        <v>-2.867706206548852</v>
+        <v>-2.037977796106547</v>
       </c>
       <c r="G98">
-        <v>0.7086211220126637</v>
+        <v>-0.5380177695285302</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.950149475708067</v>
       </c>
       <c r="E99">
-        <v>-38.12933660168331</v>
+        <v>-40.39678882206393</v>
       </c>
       <c r="F99">
-        <v>-3.22210828922337</v>
+        <v>-2.368071437345913</v>
       </c>
       <c r="G99">
-        <v>-1.073025102493529</v>
+        <v>-0.8494341673166922</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.340642495870276</v>
       </c>
       <c r="E100">
-        <v>-41.80166410617452</v>
+        <v>-43.20556123989945</v>
       </c>
       <c r="F100">
-        <v>-3.243881098038552</v>
+        <v>-2.568141217572258</v>
       </c>
       <c r="G100">
-        <v>-0.783779428181866</v>
+        <v>-2.116505745926268</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.730041917670689</v>
       </c>
       <c r="E101">
-        <v>-44.97884373419304</v>
+        <v>-44.08607772595087</v>
       </c>
       <c r="F101">
-        <v>-3.256087920086206</v>
+        <v>-2.565955984363673</v>
       </c>
       <c r="G101">
-        <v>-0.4046623741156082</v>
+        <v>-2.249500291875409</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.017506891495487</v>
       </c>
       <c r="E102">
-        <v>-45.6121825234838</v>
+        <v>-46.18057846703055</v>
       </c>
       <c r="F102">
-        <v>-3.574735180553689</v>
+        <v>-2.784129734178201</v>
       </c>
       <c r="G102">
-        <v>-2.246295683793395</v>
+        <v>-2.494626325785205</v>
       </c>
     </row>
   </sheetData>
